--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486367_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486367_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8234</v>
+        <v>2.7038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5557</v>
+        <v>0.2205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2676</v>
+        <v>2.4834</v>
       </c>
       <c r="G2" t="n">
         <v>1.4385</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2671</v>
+        <v>-0.3866</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6682</v>
+        <v>0.3329</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9353</v>
+        <v>-0.7195</v>
       </c>
       <c r="V2" t="n">
         <v>1.8695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5126</v>
+        <v>1.8306</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2451</v>
+        <v>0.6863</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2675</v>
+        <v>1.1442</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3303</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9729</v>
+        <v>0.2908</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6802</v>
+        <v>0.1214</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2927</v>
+        <v>0.1694</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6131</v>
+        <v>1.5938</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7469</v>
+        <v>1.6351</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1338</v>
+        <v>-0.0413</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2791</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3272</v>
+        <v>0.3079</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4146</v>
+        <v>0.3028</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V4" t="n">
         <v>1.695</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5524</v>
+        <v>0.3289</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3472</v>
+        <v>2.1237</v>
       </c>
       <c r="F5" t="n">
         <v>-1.7948</v>
@@ -844,10 +844,10 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0311</v>
+        <v>0.8075</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6201</v>
+        <v>0.3966</v>
       </c>
       <c r="U5" t="n">
         <v>0.411</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4857</v>
+        <v>-0.2722</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7867</v>
+        <v>-1.0132</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2725</v>
+        <v>0.741</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5894</v>
+        <v>1.7482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6173</v>
+        <v>2.1107</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0279</v>
+        <v>-0.3626</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0437</v>
+        <v>1.7093</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9671999999999999</v>
+        <v>2.032</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>-0.3227</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4543</v>
+        <v>0.0389</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3499</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1044</v>
+        <v>-0.0399</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2501</v>
+        <v>-0.015</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2656</v>
+        <v>0.3449</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0155</v>
+        <v>-0.3599</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3252</v>
+        <v>-0.4828</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8902</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.646</v>
+        <v>-0.6784</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.572</v>
+        <v>0.5632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.926</v>
+        <v>-1.2416</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7482</v>
+        <v>0.5894</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1107</v>
+        <v>0.6173</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3626</v>
+        <v>-0.0279</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7093</v>
+        <v>1.0437</v>
       </c>
       <c r="K7" t="n">
-        <v>2.032</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3227</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0389</v>
+        <v>-0.4543</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.3499</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0399</v>
+        <v>-0.1044</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3889</v>
+        <v>0.0574</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2139</v>
+        <v>0.0421</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.175</v>
+        <v>0.0153</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4828</v>
+        <v>-1.3252</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.678</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4787</v>
+        <v>-2.051</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5231</v>
+        <v>-0.1878</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9556</v>
+        <v>-1.8632</v>
       </c>
       <c r="G8" t="n">
         <v>0.2023</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4863</v>
+        <v>-0.0586</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>-0.1322</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0189</v>
+        <v>0.0736</v>
       </c>
       <c r="V8" t="n">
         <v>-2.6297</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6435</v>
+        <v>-2.4642</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8607</v>
+        <v>-1.7431</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.7212</v>
       </c>
       <c r="G9" t="n">
         <v>2.3072</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2075</v>
+        <v>-0.0282</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>0.3076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3975</v>
+        <v>-0.3359</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5682</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.707</v>
+        <v>-3.4296</v>
       </c>
       <c r="E10" t="n">
         <v>-2.1566</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5504</v>
+        <v>-1.273</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7073</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.649</v>
+        <v>-0.3716</v>
       </c>
       <c r="T10" t="n">
         <v>0.3257</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9747</v>
+        <v>-0.6973</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2245</v>
+        <v>-4.4673</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9258</v>
+        <v>-5.2611</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7013</v>
+        <v>0.7937</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7502</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3957</v>
+        <v>0.1529</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3341</v>
+        <v>-0.0012</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.229</v>
+        <v>-6.0074</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3654</v>
+        <v>-2.5889</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8637</v>
+        <v>-3.4185</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1732</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2296</v>
+        <v>0.4512</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7367</v>
+        <v>0.5131</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4929</v>
+        <v>-0.0619</v>
       </c>
       <c r="V12" t="n">
         <v>-4.0679</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.9129</v>
+        <v>-12.913</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.722</v>
+        <v>-7.721900000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.1912</v>
+        <v>-5.1913</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8204000000000002</v>
@@ -1468,13 +1468,13 @@
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2078</v>
+        <v>1.2077</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5539</v>
+        <v>2.5537</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3461</v>
+        <v>-1.346</v>
       </c>
       <c r="V13" t="n">
         <v>-11.1252</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8582</v>
+        <v>6.8202</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9913</v>
+        <v>5.6502</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8668</v>
+        <v>1.17</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7359</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3994</v>
+        <v>0.3614</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2508</v>
+        <v>0.9097</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8514</v>
+        <v>-0.5483</v>
       </c>
       <c r="V14" t="n">
         <v>6.0196</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7094</v>
+        <v>5.7865</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9447</v>
+        <v>4.3917</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7647</v>
+        <v>1.3948</v>
       </c>
       <c r="G15" t="n">
         <v>5.2424</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2293</v>
+        <v>0.3064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7652</v>
+        <v>0.3953</v>
       </c>
       <c r="V15" t="n">
         <v>1.3252</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9377</v>
+        <v>2.3713</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2579</v>
+        <v>1.3696</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6798</v>
+        <v>1.0017</v>
       </c>
       <c r="G16" t="n">
         <v>2.1021</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8133</v>
+        <v>0.2469</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1558</v>
+        <v>0.4777</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8987</v>
+        <v>2.2867</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0453</v>
+        <v>-0.3747</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9439</v>
+        <v>2.6614</v>
       </c>
       <c r="G17" t="n">
         <v>0.3575</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5893</v>
+        <v>-0.2013</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0024</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.1989</v>
       </c>
       <c r="V17" t="n">
         <v>0.3904</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0745</v>
+        <v>1.5606</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5335</v>
+        <v>1.1581</v>
       </c>
       <c r="F18" t="n">
-        <v>0.541</v>
+        <v>0.4025</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2566</v>
+        <v>-0.9922</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9123</v>
+        <v>-2.8648</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3442</v>
+        <v>1.8726</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3027</v>
+        <v>-0.7147</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5959</v>
+        <v>-1.137</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7068</v>
+        <v>0.4224</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0461</v>
+        <v>-0.2776</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3164</v>
+        <v>-1.7278</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3626</v>
+        <v>1.4502</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2435</v>
+        <v>-0.1199</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8362</v>
+        <v>0.4627</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5927</v>
+        <v>-0.5825</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.5851</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7745</v>
+        <v>0.7254</v>
       </c>
       <c r="E19" t="n">
-        <v>0.711</v>
+        <v>0.4042</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0635</v>
+        <v>0.3212</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9922</v>
+        <v>0.0274</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8648</v>
+        <v>-0.3591</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8726</v>
+        <v>0.3865</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7147</v>
+        <v>0.669</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.137</v>
+        <v>0.4562</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4224</v>
+        <v>0.2128</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2776</v>
+        <v>-0.6417</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7278</v>
+        <v>-0.8153</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4502</v>
+        <v>0.1737</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.906</v>
+        <v>-0.3019</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0156</v>
+        <v>-0.3497</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9216</v>
+        <v>0.0478</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4552</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>3.5851</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2361</v>
+        <v>-0.0675</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0689</v>
+        <v>-0.6958</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1671</v>
+        <v>0.6284</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0274</v>
+        <v>-1.2566</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3591</v>
+        <v>-0.9123</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3865</v>
+        <v>-0.3442</v>
       </c>
       <c r="J20" t="n">
-        <v>0.669</v>
+        <v>-1.3027</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4562</v>
+        <v>-0.5959</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2128</v>
+        <v>-0.7068</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6417</v>
+        <v>0.0461</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8153</v>
+        <v>-0.3164</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1737</v>
+        <v>0.3626</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7913</v>
+        <v>0.1015</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.6069</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1064</v>
+        <v>-0.5053</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9429</v>
+        <v>-0.1504</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1625</v>
+        <v>-1.8273</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2197</v>
+        <v>1.6769</v>
       </c>
       <c r="G21" t="n">
         <v>1.2442</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.882</v>
+        <v>-0.0895</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1935</v>
+        <v>0.1418</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6886</v>
+        <v>-0.2313</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5279</v>
+        <v>-0.7238</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2068</v>
+        <v>-0.9833</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3211</v>
+        <v>0.2594</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0159</v>
@@ -2170,13 +2170,13 @@
         <v>3.2626</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4043</v>
+        <v>-0.6002</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0529</v>
+        <v>0.1707</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3514</v>
+        <v>-0.7709</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1052</v>
+        <v>-4.951</v>
       </c>
       <c r="E23" t="n">
         <v>-3.9016</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2036</v>
+        <v>-1.0495</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1525</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3203</v>
+        <v>-0.1661</v>
       </c>
       <c r="T23" t="n">
         <v>-0.274</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V23" t="n">
         <v>0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.9131</v>
+        <v>13.658</v>
       </c>
       <c r="E24" t="n">
         <v>5.1911</v>
       </c>
       <c r="F24" t="n">
-        <v>7.721800000000002</v>
+        <v>8.466799999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.8205</v>
@@ -2326,13 +2326,13 @@
         <v>18.4881</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2077</v>
+        <v>-0.4627</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3458</v>
+        <v>1.3461</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5538</v>
+        <v>-1.8086</v>
       </c>
       <c r="V24" t="n">
         <v>11.1252</v>
